--- a/model_calibration.xlsx
+++ b/model_calibration.xlsx
@@ -586,13 +586,13 @@
         </is>
       </c>
       <c r="C6">
-        <v>1.7143</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D6">
-        <v>1.6163</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="E6">
-        <v>1.8123</v>
+        <v>0.5428571428571428</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="H6">
-        <v>1.7143</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="J6">
-        <v>0.05</v>
+        <v>0.05830903790087461</v>
       </c>
     </row>
     <row r="7">

--- a/model_calibration.xlsx
+++ b/model_calibration.xlsx
@@ -586,34 +586,34 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.4285714285714285</v>
+        <v>0.4481253468959464</v>
       </c>
       <c r="D6">
-        <v>0.3142857142857143</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="E6">
-        <v>0.5428571428571428</v>
+        <v>0.5857142857142856</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>lognormal</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>α</t>
+          <t>meanlog</t>
         </is>
       </c>
       <c r="H6">
-        <v>0.4285714285714285</v>
+        <v>-0.8026822935232323</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>β</t>
+          <t>sdlog</t>
         </is>
       </c>
       <c r="J6">
-        <v>0.05830903790087461</v>
+        <v>0.1366117949888679</v>
       </c>
     </row>
     <row r="7">

--- a/model_calibration.xlsx
+++ b/model_calibration.xlsx
@@ -547,31 +547,31 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>0.7</v>
+        <v>0.7453600177007041</v>
       </c>
       <c r="E5">
-        <v>1.4</v>
+        <v>1.341633541177607</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>lognormal</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>α</t>
+          <t>meanlog</t>
         </is>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>β</t>
+          <t>sdlog</t>
         </is>
       </c>
       <c r="J5">
-        <v>0.17857</v>
+        <v>0.1499455777811528</v>
       </c>
     </row>
     <row r="6">
@@ -586,13 +586,13 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.4481253468959464</v>
+        <v>1.309307341415954</v>
       </c>
       <c r="D6">
-        <v>0.3428571428571429</v>
+        <v>1.000004952105854</v>
       </c>
       <c r="E6">
-        <v>0.5857142857142856</v>
+        <v>1.714277225003432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="H6">
-        <v>-0.8026822935232323</v>
+        <v>0.2694982503663435</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="J6">
-        <v>0.1366117949888679</v>
+        <v>0.1374991073297671</v>
       </c>
     </row>
     <row r="7">
